--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01171275399631736</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.0008197092010944531</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -91068,7 +91068,7 @@
         <v>0.02424554436027555</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91086,7 +91086,7 @@
         <v>113678</v>
       </c>
       <c r="K56" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57">
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>48450</v>
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01171275399631736</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.0008197092010944531</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -49641,10 +49641,10 @@
         <v>0.06204791622724848</v>
       </c>
       <c r="J56" t="n">
-        <v>14811</v>
+        <v>14858</v>
       </c>
       <c r="K56" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -91068,7 +91068,7 @@
         <v>0.02424554436027555</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91083,10 +91083,10 @@
         <v>0.06907469499195264</v>
       </c>
       <c r="J56" t="n">
-        <v>113678</v>
+        <v>113689</v>
       </c>
       <c r="K56" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57">
@@ -94616,25 +94616,25 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
-        <v>48450</v>
+        <v>48464</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>10434</v>
+        <v>10884</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-0.001915351628048884</v>
+        <v>0.005949455057036798</v>
       </c>
       <c r="J56" t="n">
-        <v>10391</v>
+        <v>10423</v>
       </c>
       <c r="K56" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -94665,7 +94665,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.281196929556416</v>
+        <v>-0.2868167419289614</v>
       </c>
       <c r="J57" t="n">
         <v>1918</v>
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01171275399631736</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.0008197092010944531</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -91059,16 +91059,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1877498</v>
+        <v>1877769</v>
       </c>
       <c r="C56" t="n">
         <v>44382</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.02424554436027555</v>
+        <v>0.02438997093348597</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91102,7 +91102,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.2269621412367057</v>
+        <v>-0.2270711302077724</v>
       </c>
       <c r="E57" t="n">
         <v>8</v>
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01171275399631736</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.0008197092010944531</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -91068,7 +91068,7 @@
         <v>0.02438997093348597</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15062,16 +15062,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>308843</v>
+        <v>308667</v>
       </c>
       <c r="C56" t="n">
         <v>1596</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.01171275399631736</v>
+        <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -15105,7 +15105,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.3010897471000744</v>
+        <v>-0.3006932827955638</v>
       </c>
       <c r="E57" t="n">
         <v>8</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.0008197092010944531</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -87529,10 +87529,10 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>6273</v>
+        <v>9719</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.461605775541457</v>
+        <v>0.7129001677240575</v>
       </c>
       <c r="J56" t="n">
         <v>1757</v>
@@ -87569,7 +87569,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.01870977398593025</v>
+        <v>-0.1626718889693048</v>
       </c>
       <c r="J57" t="n">
         <v>1701</v>
@@ -91059,16 +91059,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1877769</v>
+        <v>1877746</v>
       </c>
       <c r="C56" t="n">
         <v>44382</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.02438997093348597</v>
+        <v>0.02437771332764154</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91083,10 +91083,10 @@
         <v>0.06907469499195264</v>
       </c>
       <c r="J56" t="n">
-        <v>113689</v>
+        <v>113728</v>
       </c>
       <c r="K56" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -91102,7 +91102,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.2270711302077724</v>
+        <v>-0.2270618814147653</v>
       </c>
       <c r="E57" t="n">
         <v>8</v>
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -15086,7 +15086,7 @@
         <v>0.2251658961537252</v>
       </c>
       <c r="J56" t="n">
-        <v>16577</v>
+        <v>16584</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -22182,7 +22182,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>10606</v>
+        <v>10611</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49617,16 +49617,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>177037</v>
+        <v>177311</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.0008197092010944531</v>
+        <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -49641,7 +49641,7 @@
         <v>0.06204791622724848</v>
       </c>
       <c r="J56" t="n">
-        <v>14858</v>
+        <v>14860</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -49660,7 +49660,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.1598309957805431</v>
+        <v>-0.161129315158112</v>
       </c>
       <c r="E57" t="n">
         <v>8</v>
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -87529,10 +87529,10 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>9719</v>
+        <v>10037</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.7129001677240575</v>
+        <v>0.736089841755998</v>
       </c>
       <c r="J56" t="n">
         <v>1757</v>
@@ -87569,7 +87569,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.1626718889693048</v>
+        <v>-0.1738564287814508</v>
       </c>
       <c r="J57" t="n">
         <v>1701</v>
@@ -91068,7 +91068,7 @@
         <v>0.02437771332764154</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91086,7 +91086,7 @@
         <v>113728</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -15086,10 +15086,10 @@
         <v>0.2251658961537252</v>
       </c>
       <c r="J56" t="n">
-        <v>16584</v>
+        <v>16590</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -49644,7 +49644,7 @@
         <v>14860</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -91068,7 +91068,7 @@
         <v>0.02437771332764154</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91083,10 +91083,10 @@
         <v>0.06907469499195264</v>
       </c>
       <c r="J56" t="n">
-        <v>113728</v>
+        <v>113887</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -94631,10 +94631,10 @@
         <v>0.005949455057036798</v>
       </c>
       <c r="J56" t="n">
-        <v>10423</v>
+        <v>10425</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -7993,7 +7993,7 @@
         <v>6821</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -22185,7 +22185,7 @@
         <v>10611</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -49644,7 +49644,7 @@
         <v>14860</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -91068,7 +91068,7 @@
         <v>0.02437771332764154</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91086,7 +91086,7 @@
         <v>113887</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -94634,7 +94634,7 @@
         <v>10425</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -15089,7 +15089,7 @@
         <v>16590</v>
       </c>
       <c r="K56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -22185,7 +22185,7 @@
         <v>10611</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -49644,7 +49644,7 @@
         <v>14860</v>
       </c>
       <c r="K56" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -91068,7 +91068,7 @@
         <v>0.02437771332764154</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91086,7 +91086,7 @@
         <v>113887</v>
       </c>
       <c r="K56" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -94634,7 +94634,7 @@
         <v>10425</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -15089,7 +15089,7 @@
         <v>16590</v>
       </c>
       <c r="K56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -49644,7 +49644,7 @@
         <v>14860</v>
       </c>
       <c r="K56" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -91068,7 +91068,7 @@
         <v>0.02437771332764154</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91086,7 +91086,7 @@
         <v>113887</v>
       </c>
       <c r="K56" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57">
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -94634,7 +94634,7 @@
         <v>10425</v>
       </c>
       <c r="K56" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -22182,10 +22182,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>10611</v>
+        <v>10615</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -49644,7 +49644,7 @@
         <v>14860</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -91068,7 +91068,7 @@
         <v>0.02437771332764154</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91077,16 +91077,16 @@
         <v>98654</v>
       </c>
       <c r="H56" t="n">
-        <v>27391</v>
+        <v>28725</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.06907469499195264</v>
+        <v>0.06997757025032791</v>
       </c>
       <c r="J56" t="n">
-        <v>113887</v>
+        <v>113952</v>
       </c>
       <c r="K56" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -91117,7 +91117,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.528585808706222</v>
+        <v>-0.5289836004184973</v>
       </c>
       <c r="J57" t="n">
         <v>76849</v>
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -94631,10 +94631,10 @@
         <v>0.005949455057036798</v>
       </c>
       <c r="J56" t="n">
-        <v>10425</v>
+        <v>10438</v>
       </c>
       <c r="K56" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -7993,7 +7993,7 @@
         <v>6821</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -22185,7 +22185,7 @@
         <v>10615</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -49644,7 +49644,7 @@
         <v>14860</v>
       </c>
       <c r="K56" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -91068,7 +91068,7 @@
         <v>0.02437771332764154</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91086,7 +91086,7 @@
         <v>113952</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -94634,7 +94634,7 @@
         <v>10438</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         <v>0.005796011370800934</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>21269</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -13110,7 +13110,7 @@
         <v>0.02565686080219745</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>78549</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -16658,7 +16658,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20206,7 +20206,7 @@
         <v>0.008444826477516551</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>16252</v>
@@ -22167,7 +22167,7 @@
         <v>4.120288891112537e-05</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -23754,7 +23754,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -27265,7 +27265,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -30147,7 +30147,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -33695,7 +33695,7 @@
         <v>0.001128158844765343</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -37243,7 +37243,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -40791,7 +40791,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -44117,7 +44117,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -47665,7 +47665,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>47141</v>
@@ -49626,7 +49626,7 @@
         <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -51176,7 +51176,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -54058,7 +54058,7 @@
         <v>0.05192696525948165</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>6217</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -57606,7 +57606,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -61154,7 +61154,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -64702,7 +64702,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -68028,7 +68028,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -71576,7 +71576,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -75124,7 +75124,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -78672,7 +78672,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -82011,7 +82011,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -85559,7 +85559,7 @@
         <v>0.05729804161566707</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>13457</v>
@@ -87520,7 +87520,7 @@
         <v>0.02995586988923634</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>13770</v>
@@ -89107,7 +89107,7 @@
         <v>0.09443507924420068</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>1351324</v>
@@ -91068,7 +91068,7 @@
         <v>0.02437771332764154</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -92655,7 +92655,7 @@
         <v>0.007811848433460287</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>48033</v>
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -96203,7 +96203,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -99751,7 +99751,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         <v>0.005796011370800934</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>21269</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -7990,10 +7990,10 @@
         <v>0.7351286566872126</v>
       </c>
       <c r="J56" t="n">
-        <v>6821</v>
+        <v>6845</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -9562,7 +9562,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -11538,7 +11538,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -13110,7 +13110,7 @@
         <v>0.02565686080219745</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>78549</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -15086,10 +15086,10 @@
         <v>0.2251658961537252</v>
       </c>
       <c r="J56" t="n">
-        <v>16590</v>
+        <v>16612</v>
       </c>
       <c r="K56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -16658,7 +16658,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -20206,7 +20206,7 @@
         <v>0.008444826477516551</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>16252</v>
@@ -22158,16 +22158,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>169898</v>
+        <v>170733</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>4.120288891112537e-05</v>
+        <v>0.004956118923309652</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -22182,10 +22182,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>10615</v>
+        <v>10626</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -22201,7 +22201,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.1029853206041272</v>
+        <v>-0.1073723298952165</v>
       </c>
       <c r="E57" t="n">
         <v>8</v>
@@ -23754,7 +23754,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -27265,7 +27265,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -30147,7 +30147,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -33695,7 +33695,7 @@
         <v>0.001128158844765343</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -37243,7 +37243,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -40791,7 +40791,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -44117,7 +44117,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -46069,16 +46069,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31953</v>
+        <v>32842</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.02782211372954026</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -46093,7 +46093,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -46112,7 +46112,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.3019747754514443</v>
+        <v>-0.3208696181718531</v>
       </c>
       <c r="E57" t="n">
         <v>8</v>
@@ -47665,7 +47665,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>47141</v>
@@ -49626,7 +49626,7 @@
         <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -49641,10 +49641,10 @@
         <v>0.06204791622724848</v>
       </c>
       <c r="J56" t="n">
-        <v>14860</v>
+        <v>14921</v>
       </c>
       <c r="K56" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -51176,7 +51176,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -54058,7 +54058,7 @@
         <v>0.05192696525948165</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>6217</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -56034,7 +56034,7 @@
         <v>1.649328600092607</v>
       </c>
       <c r="J56" t="n">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -57606,7 +57606,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -59582,7 +59582,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -61154,7 +61154,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -64702,7 +64702,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -68028,7 +68028,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -71576,7 +71576,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73552,7 +73552,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -75124,7 +75124,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -78672,7 +78672,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -80426,7 +80426,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -82011,7 +82011,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -85559,7 +85559,7 @@
         <v>0.05729804161566707</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>13457</v>
@@ -87511,31 +87511,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>35242</v>
+        <v>35260</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.02995586988923634</v>
+        <v>0.03048192418973025</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
-        <v>13770</v>
+        <v>13828</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>10037</v>
+        <v>11606</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.736089841755998</v>
+        <v>0.854736381535769</v>
       </c>
       <c r="J56" t="n">
-        <v>1757</v>
+        <v>1762</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -87554,7 +87554,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.3049486408262868</v>
+        <v>-0.3053034600113443</v>
       </c>
       <c r="E57" t="n">
         <v>8</v>
@@ -87569,7 +87569,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.1738564287814508</v>
+        <v>-0.2267044114177872</v>
       </c>
       <c r="J57" t="n">
         <v>1701</v>
@@ -89107,7 +89107,7 @@
         <v>0.09443507924420068</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>1351324</v>
@@ -91059,16 +91059,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1877746</v>
+        <v>1877694</v>
       </c>
       <c r="C56" t="n">
-        <v>44382</v>
+        <v>44543</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.02437771332764154</v>
+        <v>0.02443580372055643</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91083,10 +91083,10 @@
         <v>0.06997757025032791</v>
       </c>
       <c r="J56" t="n">
-        <v>113952</v>
+        <v>114176</v>
       </c>
       <c r="K56" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -91102,7 +91102,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.2270618814147653</v>
+        <v>-0.2271057106902011</v>
       </c>
       <c r="E57" t="n">
         <v>8</v>
@@ -92655,7 +92655,7 @@
         <v>0.007811848433460287</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>48033</v>
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -94631,10 +94631,10 @@
         <v>0.005949455057036798</v>
       </c>
       <c r="J56" t="n">
-        <v>10438</v>
+        <v>10448</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -96203,7 +96203,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -98179,7 +98179,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -99751,7 +99751,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101727,7 +101727,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>0.004956118923309652</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0.02782211372954026</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.03048192418973025</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>13828</v>
@@ -91068,7 +91068,7 @@
         <v>0.02443580372055643</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91083,10 +91083,10 @@
         <v>0.06997757025032791</v>
       </c>
       <c r="J56" t="n">
-        <v>114176</v>
+        <v>114179</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>0.004956118923309652</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0.02782211372954026</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.03048192418973025</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>13828</v>
@@ -91068,7 +91068,7 @@
         <v>0.02443580372055643</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroDOS.xlsx
+++ b/regionais/registroDOS.xlsx
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0.02640392988723903</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>39913</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -15071,7 +15071,7 @@
         <v>0.01113917450178429</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>143328</v>
@@ -15086,7 +15086,7 @@
         <v>0.2251658961537252</v>
       </c>
       <c r="J56" t="n">
-        <v>16612</v>
+        <v>16613</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>0.004956118923309652</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>64504</v>
@@ -22182,7 +22182,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>10626</v>
+        <v>10625</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28782,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -32108,7 +32108,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -35656,7 +35656,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42530,7 +42530,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -46078,7 +46078,7 @@
         <v>0.02782211372954026</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49626,7 +49626,7 @@
         <v>0.002368676932817765</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>70254</v>
@@ -49641,7 +49641,7 @@
         <v>0.06204791622724848</v>
       </c>
       <c r="J56" t="n">
-        <v>14921</v>
+        <v>14919</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -52693,7 +52693,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -56019,7 +56019,7 @@
         <v>0.007467235598902774</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>6598</v>
@@ -59567,7 +59567,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -63115,7 +63115,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -66441,7 +66441,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -69989,7 +69989,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -73537,7 +73537,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -77085,7 +77085,7 @@
         <v>0.01220077771039207</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -80411,7 +80411,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -83972,7 +83972,7 @@
         <v>0.001303008765695333</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -87520,7 +87520,7 @@
         <v>0.03048192418973025</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>13828</v>
@@ -91068,7 +91068,7 @@
         <v>0.02443580372055643</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>1453515</v>
@@ -91083,7 +91083,7 @@
         <v>0.06997757025032791</v>
       </c>
       <c r="J56" t="n">
-        <v>114179</v>
+        <v>114180</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -94616,7 +94616,7 @@
         <v>0.02557850561507983</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>48464</v>
@@ -94631,7 +94631,7 @@
         <v>0.005949455057036798</v>
       </c>
       <c r="J56" t="n">
-        <v>10448</v>
+        <v>10449</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -98164,7 +98164,7 @@
         <v>0.03307027433295753</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -101712,7 +101712,7 @@
         <v>0.01531702204845016</v>
       </c>
       <c r="E56" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
